--- a/content/channels.xlsx
+++ b/content/channels.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>id</t>
   </si>
@@ -31,6 +31,9 @@
     <t>资质最大</t>
   </si>
   <si>
+    <t>卡池id</t>
+  </si>
+  <si>
     <t>文案</t>
   </si>
   <si>
@@ -43,6 +46,9 @@
     <t>dance,acting</t>
   </si>
   <si>
+    <t>pool-comic</t>
+  </si>
+  <si>
     <t>在人堆里挤了一天，加到了几个同好。</t>
   </si>
   <si>
@@ -55,6 +61,9 @@
     <t>vocal,dance</t>
   </si>
   <si>
+    <t>pool-stage</t>
+  </si>
+  <si>
     <t>散场后在后门等到很晚，认识了两个同样在练的人。</t>
   </si>
   <si>
@@ -65,6 +74,9 @@
   </si>
   <si>
     <t>vocal,dance,acting,talk</t>
+  </si>
+  <si>
+    <t>pool-intro</t>
   </si>
   <si>
     <t>朋友把她拉进群，说了句「你们应该聊得来」。</t>
@@ -453,15 +465,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="4" width="14" customWidth="1"/>
-    <col min="5" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="5" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -483,19 +495,22 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2">
         <v>200</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2">
         <v>0.8</v>
@@ -504,21 +519,24 @@
         <v>1.05</v>
       </c>
       <c r="G2" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="H2" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C3">
         <v>300</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E3">
         <v>0.85</v>
@@ -527,21 +545,24 @@
         <v>1.1</v>
       </c>
       <c r="G3" t="s">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="H3" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C4">
         <v>500</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E4">
         <v>0.95</v>
@@ -550,7 +571,10 @@
         <v>1.15</v>
       </c>
       <c r="G4" t="s">
-        <v>18</v>
+        <v>21</v>
+      </c>
+      <c r="H4" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
